--- a/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Rapeseed Oil (1514.11)/U.S.A.xlsx
+++ b/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Rapeseed Oil (1514.11)/U.S.A.xlsx
@@ -3900,7 +3900,7 @@
         <v>622</v>
       </c>
       <c r="F4" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -4055,13 +4055,14 @@
       </c>
       <c r="F15" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
